--- a/Configs/GameConfig/Datas/economy.xlsx
+++ b/Configs/GameConfig/Datas/economy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,16 @@
           <t>handSize</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>playerMaxHealth</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>opponentMaxHealth</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,67 +489,94 @@
           <t>int</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>玩家方最大生命</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>对手方最大生命</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>初始金币</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>刷新起始消耗</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>刷新递增</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>单位基础消耗</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>手牌数</t>
+          <t>##group</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>初始金币</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>刷新起始消耗</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>刷新递增</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>单位基础消耗</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>手牌数</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
         <v>20</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" t="n">
         <v>10</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/economy.xlsx
+++ b/Configs/GameConfig/Datas/economy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf94023b4cc6e46c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb07059392b5b4370"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -349,12 +349,8 @@
       <x:c r="G1" t="str">
         <x:v>handSize</x:v>
       </x:c>
-      <x:c r="H1" t="str">
-        <x:v>playerMaxHealth</x:v>
-      </x:c>
-      <x:c r="I1" t="str">
-        <x:v>opponentMaxHealth</x:v>
-      </x:c>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -378,29 +374,33 @@
       <x:c r="G2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="H2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="I2" t="str">
-        <x:v>int</x:v>
-      </x:c>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3"/>
-      <x:c r="C3"/>
-      <x:c r="D3"/>
-      <x:c r="E3"/>
-      <x:c r="F3"/>
-      <x:c r="G3"/>
-      <x:c r="H3" t="str">
-        <x:v>玩家方最大生命</x:v>
-      </x:c>
-      <x:c r="I3" t="str">
-        <x:v>对手方最大生命</x:v>
-      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>占位</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>开局金币</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>首次刷新费用</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>每次刷新递增的费用</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>基础招募/单位费用</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>手牌数量</x:v>
+      </x:c>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -419,24 +419,12 @@
       <x:c r="A5" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B5" t="str">
-        <x:v>ID(主键)</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>初始金币</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>刷新起始消耗</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>刷新递增</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
-        <x:v>单位基础消耗</x:v>
-      </x:c>
-      <x:c r="G5" t="str">
-        <x:v>手牌数</x:v>
-      </x:c>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
       <x:c r="H5"/>
       <x:c r="I5"/>
     </x:row>
@@ -460,12 +448,8 @@
       <x:c r="G6" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I6" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
